--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129574798</v>
       </c>
       <c r="B3" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129574782</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129574798</v>
       </c>
       <c r="B3" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129574782</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129574798</v>
       </c>
       <c r="B3" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129574782</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129574798</v>
       </c>
       <c r="B3" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129574782</v>
       </c>
       <c r="B4" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129574798</v>
       </c>
       <c r="B3" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129574782</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129574798</v>
       </c>
       <c r="B3" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129574782</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129574798</v>
       </c>
       <c r="B3" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129574782</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129574798</v>
       </c>
       <c r="B3" t="n">
-        <v>92255</v>
+        <v>92258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129574782</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129574799</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>129574800</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>129574801</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -757,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129579858</v>
+        <v>129574782</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO Lövstan, NO Lövstan, Srm</t>
+          <t>NO Lövstan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621296</v>
+        <v>621297</v>
       </c>
       <c r="R2" t="n">
-        <v>6557284</v>
+        <v>6557182</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -770,39 +772,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Gustaf Eibl, Jonna Rennerskog</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129574798</v>
+        <v>129823721</v>
       </c>
       <c r="B3" t="n">
-        <v>92258</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,20 +814,19 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO Lövstan, Srm</t>
+          <t>Lövstan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621303</v>
+        <v>621272</v>
       </c>
       <c r="R3" t="n">
-        <v>6557274</v>
+        <v>6557157</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,39 +876,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gustaf Eibl, Jonna Rennerskog</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129574782</v>
+        <v>129574798</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621297</v>
+        <v>621303</v>
       </c>
       <c r="R4" t="n">
-        <v>6557182</v>
+        <v>6557274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,53 +987,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129574799</v>
+        <v>129823698</v>
       </c>
       <c r="B5" t="n">
-        <v>8440</v>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NO Lövstan, Srm</t>
+          <t>Lövstan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621313</v>
+        <v>621359</v>
       </c>
       <c r="R5" t="n">
-        <v>6557255</v>
+        <v>6557177</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,17 +1077,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gustaf Eibl, Jonna Rennerskog</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129574800</v>
+        <v>129579858</v>
       </c>
       <c r="B6" t="n">
-        <v>8440</v>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,42 +1095,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NO Lövstan, Srm</t>
+          <t>NO Lövstan, NO Lövstan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621286</v>
+        <v>621296</v>
       </c>
       <c r="R6" t="n">
-        <v>6557320</v>
+        <v>6557284</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1182,17 +1179,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gustaf Eibl, Jonna Rennerskog</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129574801</v>
+        <v>129574799</v>
       </c>
       <c r="B7" t="n">
-        <v>8440</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621315</v>
+        <v>621313</v>
       </c>
       <c r="R7" t="n">
-        <v>6557290</v>
+        <v>6557255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1285,210 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129574800</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO Lövstan, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>621286</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6557320</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl, Jonna Rennerskog</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129574801</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO Lövstan, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>621315</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6557290</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl, Jonna Rennerskog</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49248-2025 artfynd.xlsx
+++ b/artfynd/A 49248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574782</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129823721</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574798</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129823698</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129579858</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574799</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574800</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,8 +1529,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574801</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>